--- a/data/Event_Data_NNB02VR-102.xlsx
+++ b/data/Event_Data_NNB02VR-102.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23-09-2569 00:34</t>
+          <t>13-10-2569 03:25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -468,14 +468,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17-09-2569 17:57</t>
+          <t>23-09-2569 00:34</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15-09-2569 13:52</t>
+          <t>17-09-2569 17:57</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -512,14 +512,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06-09-2569 23:27</t>
+          <t>15-09-2569 13:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -529,19 +529,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>T/L กิ่งไม้หักพาดสายแรงสูง 50 ACSR เฟส A B บริเวณ บ.โพนแพง อ.ธาตพนม ห่าง R 10 กม.</t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>29-07-2569 09:12</t>
+          <t>06-09-2569 23:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,19 +551,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/L กิ่งไม้หักพาดสายแรงสูง 50 ACSR เฟส A B บริเวณ บ.โพนแพง อ.ธาตพนม ห่าง R 10 กม.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14-07-2569 09:42</t>
+          <t>29-07-2569 09:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -578,14 +578,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13-07-2569 01:55</t>
+          <t>14-07-2569 09:42</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08-07-2569 20:14</t>
+          <t>13-07-2569 01:55</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -622,14 +622,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>23-06-2569 13:13</t>
+          <t>08-07-2569 20:14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -644,14 +644,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>22-06-2569 18:38</t>
+          <t>23-06-2569 13:13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -666,14 +666,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18-06-2569 16:50</t>
+          <t>22-06-2569 18:38</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,19 +683,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>T/L ต้นยางล้มพาดสายแรงสูง 50 ACSR เฟส ABC หน้า ร.ร.บ้านโพนแพง ห่าง R = 12 กม. จ่ายไฟ 17.42</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14-06-2569 23:42</t>
+          <t>18-06-2569 16:50</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,19 +705,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/L ต้นยางล้มพาดสายแรงสูง 50 ACSR เฟส ABC หน้า ร.ร.บ้านโพนแพง ห่าง R = 12 กม. จ่ายไฟ 17.42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13-06-2569 19:04</t>
+          <t>14-06-2569 23:42</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08-06-2569 03:46</t>
+          <t>13-06-2569 19:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02-06-2569 19:57</t>
+          <t>08-06-2569 03:46</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>28-05-2569 17:12</t>
+          <t>02-06-2569 19:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -798,14 +798,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ  </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01-05-2569 09:38</t>
+          <t>28-05-2569 17:12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -820,14 +820,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ  </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>24-04-2569 03:13</t>
+          <t>01-05-2569 09:38</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -849,7 +849,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19-04-2569 09:19</t>
+          <t>24-04-2569 03:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05-04-2569 09:30</t>
+          <t>19-04-2569 09:19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04-04-2569 17:31</t>
+          <t>05-04-2569 09:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>03-04-2569 13:04</t>
+          <t>04-04-2569 17:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -937,20 +937,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>03-04-2569 13:04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NNB02VR-102</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>T/R</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>T/R ไม่ทราบสาเหตุ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>29-03-2569 04:00</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>NNB02VR-102</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NNB02VR-102</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>T/L</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>T/L ซ๊อตนกเค้าแมว เฟส B สาย 185 SAC บ้านนาท่อนทุ่ง ห่าง R = 1.5 กม. จ่ายไฟ 05.12</t>
         </is>
